--- a/data/trans_dic/P22$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,26</t>
+          <t>0,11; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,37 +872,37 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,57</t>
+          <t>0,06; 0,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,75</t>
+          <t>0,09; 0,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,4</t>
+          <t>0,05; 0,36</t>
         </is>
       </c>
     </row>
@@ -997,47 +997,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,19</t>
+          <t>0,0; 0,23</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,38</t>
+          <t>0,13; 1,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,77</t>
+          <t>0,06; 0,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,66</t>
+          <t>0,06; 0,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,45</t>
+          <t>0,07; 0,44</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,46</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,29</t>
+          <t>0,04; 0,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,45</t>
+          <t>0,07; 0,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,19</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,18</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>0,02; 0,25</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,19</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,25</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,34</t>
+          <t>0,07; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,26</t>
+          <t>0,05; 0,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,18</t>
+          <t>0,02; 0,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,27</t>
+          <t>0,07; 0,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,23</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4380</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2056</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4628</t>
+          <t>0; 4297</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2030</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4269</t>
+          <t>0; 4833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 4823</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1034; 12142</t>
+          <t>1041; 13004</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 10546</t>
+          <t>0; 10544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5214</t>
+          <t>0; 6578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5974</t>
+          <t>0; 6784</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5999</t>
+          <t>0; 6581</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7259</t>
+          <t>0; 7047</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>605; 5494</t>
+          <t>614; 5927</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1655; 14434</t>
+          <t>1762; 15524</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6726</t>
+          <t>0; 6361</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 9835</t>
+          <t>0; 9966</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1196; 8534</t>
+          <t>1012; 7818</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8216</t>
+          <t>0; 9824</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8519</t>
+          <t>0; 8619</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2114</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5408</t>
+          <t>0; 7537</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 4087</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 8219</t>
+          <t>0; 7501</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 7406</t>
+          <t>0; 7303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5456</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>0; 3748</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1818</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6439</t>
+          <t>0; 7576</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1506; 12956</t>
+          <t>1231; 13059</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4760</t>
+          <t>0; 3768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4663</t>
+          <t>0; 4669</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2088</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>638; 8439</t>
+          <t>660; 8161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4649</t>
+          <t>0; 4652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6348</t>
+          <t>0; 6353</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1218; 13008</t>
+          <t>1218; 11481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1494; 9063</t>
+          <t>1342; 8886</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1652; 14932</t>
+          <t>1659; 15454</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1210; 9909</t>
+          <t>1211; 11066</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2268; 15345</t>
+          <t>2281; 14424</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>766; 8713</t>
+          <t>893; 8496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7585</t>
+          <t>0; 6450</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6591</t>
+          <t>0; 6466</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>849; 8843</t>
+          <t>850; 8879</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2888; 12462</t>
+          <t>2627; 11475</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3377; 17536</t>
+          <t>3139; 16800</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1234; 12286</t>
+          <t>1230; 12221</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4332; 18989</t>
+          <t>5010; 19820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4762; 16226</t>
+          <t>4660; 15786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,35</t>
+          <t>0,11; 1,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,59</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,64</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,68</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,62</t>
+          <t>0,07; 0,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,8</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,36</t>
+          <t>0,07; 0,43</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,23</t>
+          <t>0,0; 0,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,39</t>
+          <t>0,13; 1,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,75</t>
+          <t>0,07; 0,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,58</t>
+          <t>0,06; 0,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,44</t>
+          <t>0,09; 0,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,27 +1244,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,32</t>
+          <t>0,04; 0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,43</t>
+          <t>0,07; 0,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,25</t>
+          <t>0,03; 0,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,19</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,18</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,25</t>
+          <t>0,02; 0,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,31</t>
+          <t>0,09; 0,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,25</t>
+          <t>0,04; 0,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,17</t>
+          <t>0,02; 0,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,29</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,09; 0,29</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 4383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4297</t>
+          <t>0; 5313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4833</t>
+          <t>0; 4273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 6093</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3789</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1041; 13004</t>
+          <t>1043; 12257</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1863,52 +1863,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 10544</t>
+          <t>0; 7079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6578</t>
+          <t>0; 7867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6784</t>
+          <t>0; 6112</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6581</t>
+          <t>0; 6039</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7047</t>
+          <t>0; 6624</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>614; 5927</t>
+          <t>708; 6201</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1762; 15524</t>
+          <t>1748; 14662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6361</t>
+          <t>0; 7178</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 9966</t>
+          <t>0; 10902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1012; 7818</t>
+          <t>1436; 9111</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>708</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>708</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9824</t>
+          <t>0; 8211</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8619</t>
+          <t>0; 8572</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2091,32 +2091,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7537</t>
+          <t>0; 6972</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4087</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7501</t>
+          <t>0; 9135</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 7303</t>
+          <t>0; 8104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5418</t>
+          <t>0; 6468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3748</t>
+          <t>0; 3554</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>6027</t>
         </is>
       </c>
     </row>
@@ -2274,22 +2274,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7576</t>
+          <t>0; 7983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1231; 13059</t>
+          <t>1222; 11533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>0; 10926</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4669</t>
+          <t>0; 4668</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2304,27 +2304,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>660; 8161</t>
+          <t>758; 8561</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4652</t>
+          <t>0; 5610</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6353</t>
+          <t>0; 6339</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1218; 11481</t>
+          <t>1223; 12724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1342; 8886</t>
+          <t>1972; 13497</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>11577</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1659; 15454</t>
+          <t>1656; 15998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1211; 11066</t>
+          <t>1211; 9987</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2281; 14424</t>
+          <t>2448; 15129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>893; 8496</t>
+          <t>1142; 12727</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6450</t>
+          <t>0; 7014</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6466</t>
+          <t>0; 6855</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>850; 8879</t>
+          <t>849; 9559</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2627; 11475</t>
+          <t>3324; 13001</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3139; 16800</t>
+          <t>2864; 17250</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1230; 12221</t>
+          <t>1266; 12256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5010; 19820</t>
+          <t>4345; 17970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4660; 15786</t>
+          <t>6248; 20926</t>
         </is>
       </c>
     </row>
